--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -209,6 +209,27 @@
   </si>
   <si>
     <t>https://app.buildingconnected.com/opportunities/69bc538e7aaadb003896155f</t>
+  </si>
+  <si>
+    <t>26-0201</t>
+  </si>
+  <si>
+    <t>Adidas Tanger Deer Park</t>
+  </si>
+  <si>
+    <t>LGA</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>Joseph Dinielli</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69cd0562786a720050b13b93</t>
   </si>
 </sst>
 </file>
@@ -607,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -975,8 +996,52 @@
         <v>65</v>
       </c>
     </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" t="s">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -196,16 +196,19 @@
     <t>FINN Partners at First &amp; Main</t>
   </si>
   <si>
-    <t>Hospitality</t>
-  </si>
-  <si>
-    <t>2026-03-19</t>
+    <t>Portland (PDX)</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
   </si>
   <si>
     <t>2026-04-06</t>
   </si>
   <si>
-    <t>Jessica Howell</t>
+    <t>Automated Lead</t>
   </si>
   <si>
     <t>https://app.buildingconnected.com/opportunities/69bc538e7aaadb003896155f</t>
@@ -220,9 +223,6 @@
     <t>LGA</t>
   </si>
   <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
     <t>2026-04-08</t>
   </si>
   <si>
@@ -230,6 +230,18 @@
   </si>
   <si>
     <t>https://app.buildingconnected.com/opportunities/69cd0562786a720050b13b93</t>
+  </si>
+  <si>
+    <t>26-0202</t>
+  </si>
+  <si>
+    <t>New York (LGA)</t>
+  </si>
+  <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
   </si>
 </sst>
 </file>
@@ -628,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -960,22 +972,22 @@
         <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -993,24 +1005,24 @@
         <v>20</v>
       </c>
       <c r="N8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
         <v>70</v>
@@ -1040,8 +1052,52 @@
         <v>72</v>
       </c>
     </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>75</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -61,7 +61,7 @@
     <t>Flying Pickle Idaho Falls</t>
   </si>
   <si>
-    <t>SEA</t>
+    <t>Washington (SEA)</t>
   </si>
   <si>
     <t>Special Projects</t>
@@ -136,6 +136,9 @@
     <t>Inglewood Transit Connector RFQ</t>
   </si>
   <si>
+    <t>TM (LAX)</t>
+  </si>
+  <si>
     <t>Retail</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
   </si>
   <si>
     <t>Adidas Tanger Deer Park</t>
-  </si>
-  <si>
-    <t>LGA</t>
   </si>
   <si>
     <t>2026-04-08</t>
@@ -840,22 +840,22 @@
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
         <v>20</v>
@@ -873,18 +873,18 @@
         <v>20</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
@@ -893,19 +893,19 @@
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="s">
         <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6" t="s">
         <v>20</v>
@@ -914,36 +914,36 @@
         <v>20</v>
       </c>
       <c r="M6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
         <v>17</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
         <v>20</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
@@ -961,33 +961,33 @@
         <v>20</v>
       </c>
       <c r="N7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8" t="s">
         <v>20</v>
       </c>
       <c r="H8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
@@ -1005,24 +1005,24 @@
         <v>20</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
         <v>70</v>
@@ -1057,7 +1057,7 @@
         <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
         <v>74</v>
@@ -1066,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
         <v>70</v>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="81">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -136,7 +136,7 @@
     <t>Inglewood Transit Connector RFQ</t>
   </si>
   <si>
-    <t>TM (LAX)</t>
+    <t>LAX - FS</t>
   </si>
   <si>
     <t>Retail</t>
@@ -199,7 +199,7 @@
     <t>FINN Partners at First &amp; Main</t>
   </si>
   <si>
-    <t>Portland (PDX)</t>
+    <t>CLT - S Carolina</t>
   </si>
   <si>
     <t>Aviation</t>
@@ -214,6 +214,12 @@
     <t>Automated Lead</t>
   </si>
   <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
     <t>https://app.buildingconnected.com/opportunities/69bc538e7aaadb003896155f</t>
   </si>
   <si>
@@ -229,6 +235,9 @@
     <t>Joseph Dinielli</t>
   </si>
   <si>
+    <t>Notes for the project.</t>
+  </si>
+  <si>
     <t>https://app.buildingconnected.com/opportunities/69cd0562786a720050b13b93</t>
   </si>
   <si>
@@ -242,6 +251,9 @@
   </si>
   <si>
     <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69cd0562786a720050b13b93/info</t>
   </si>
 </sst>
 </file>
@@ -990,10 +1002,10 @@
         <v>66</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="J8" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="K8" t="s">
         <v>20</v>
@@ -1005,15 +1017,15 @@
         <v>20</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -1025,13 +1037,13 @@
         <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" t="s">
         <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
@@ -1046,21 +1058,21 @@
         <v>20</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -1069,7 +1081,7 @@
         <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -1084,16 +1096,16 @@
         <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M10" t="s">
         <v>20</v>
       </c>
       <c r="N10" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="87">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>https://app.buildingconnected.com/opportunities/69cd0562786a720050b13b93/info</t>
+  </si>
+  <si>
+    <t>Amazon SEA Legacy Space Refresh Medium GC Bid</t>
+  </si>
+  <si>
+    <t>SEA - Washington</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>Merci Keathley</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69cc472c724d4f360623c300</t>
   </si>
 </sst>
 </file>
@@ -652,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1028,7 +1046,7 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
         <v>20</v>
@@ -1108,8 +1126,52 @@
         <v>80</v>
       </c>
     </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
+        <v>85</v>
+      </c>
+      <c r="K11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N11"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -53,6 +53,105 @@
   </si>
   <si>
     <t>BC Link</t>
+  </si>
+  <si>
+    <t>26-0199</t>
+  </si>
+  <si>
+    <t>Arrowhead Regional Med Ctr. (ARMC) DB PS (REBID)</t>
+  </si>
+  <si>
+    <t>LAX</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-03-27</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>Gabriel Frota</t>
+  </si>
+  <si>
+    <t>No Bid</t>
+  </si>
+  <si>
+    <t>Automated test note</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69c6f855787ef64d5cc05edb</t>
+  </si>
+  <si>
+    <t>26-0196</t>
+  </si>
+  <si>
+    <t>Univ of Oregon - Esslinger Hall Re-roof</t>
+  </si>
+  <si>
+    <t>PDX</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>Mark Socks</t>
+  </si>
+  <si>
+    <t>Lost</t>
+  </si>
+  <si>
+    <t>NO BID - No Scope</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69c1b75e4cb9ae021994a5b7</t>
+  </si>
+  <si>
+    <t>26-0194</t>
+  </si>
+  <si>
+    <t>FINN Partners at First &amp; Main</t>
+  </si>
+  <si>
+    <t>CLT - S Carolina</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>Automated Lead</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69bc538e7aaadb003896155f</t>
+  </si>
+  <si>
+    <t>Amazon SEA Legacy Space Refresh Medium GC Bid</t>
+  </si>
+  <si>
+    <t>SEA - Washington</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>Merci Keathley</t>
+  </si>
+  <si>
+    <t>https://app.buildingconnected.com/opportunities/69cc472c724d4f360623c300</t>
   </si>
 </sst>
 </file>
@@ -451,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -511,8 +610,184 @@
         <v>13</v>
       </c>
     </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:N5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/backups/proposal-log-2026-04-01.xlsx
+++ b/backups/proposal-log-2026-04-01.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="48">
   <si>
     <t>Estimate Number</t>
   </si>
@@ -142,10 +142,13 @@
     <t>Amazon SEA Legacy Space Refresh Medium GC Bid</t>
   </si>
   <si>
-    <t>SEA - Washington</t>
+    <t>ATL - Atlanta</t>
   </si>
   <si>
     <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>HK</t>
   </si>
   <si>
     <t>Merci Keathley</t>
@@ -762,10 +765,10 @@
         <v>44</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -783,7 +786,7 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
